--- a/src/data_cleaning/data/cleaned/cleaned_no_header_invoice.xlsx
+++ b/src/data_cleaning/data/cleaned/cleaned_no_header_invoice.xlsx
@@ -14,7 +14,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="76">
+  <si>
+    <t>INV-2025-001</t>
+  </si>
+  <si>
+    <t>INV-2025-002</t>
+  </si>
+  <si>
+    <t>INV-2025-003</t>
+  </si>
   <si>
     <t>INV-2025-004</t>
   </si>
@@ -25,34 +34,34 @@
     <t>INV-2025-006</t>
   </si>
   <si>
+    <t>INV-2025-007</t>
+  </si>
+  <si>
+    <t>INV-2025-008</t>
+  </si>
+  <si>
     <t>INV-2025-009</t>
   </si>
   <si>
-    <t>INV-2025-003</t>
-  </si>
-  <si>
     <t>INV-2025-010</t>
   </si>
   <si>
-    <t>INV-2025-002</t>
-  </si>
-  <si>
     <t>INV-2025-011</t>
   </si>
   <si>
-    <t>INV-2025-007</t>
-  </si>
-  <si>
     <t>INV-2025-012</t>
   </si>
   <si>
-    <t>INV-2025-008</t>
-  </si>
-  <si>
     <t>INV-2025-013</t>
   </si>
   <si>
-    <t>INV-2025-001</t>
+    <t>TAS-001</t>
+  </si>
+  <si>
+    <t>TAS-002</t>
+  </si>
+  <si>
+    <t>TAS-003</t>
   </si>
   <si>
     <t>TAS-004</t>
@@ -64,28 +73,28 @@
     <t>TAS-007</t>
   </si>
   <si>
+    <t>TAS-008</t>
+  </si>
+  <si>
+    <t>TAS-010</t>
+  </si>
+  <si>
     <t>TAS-011</t>
   </si>
   <si>
-    <t>TAS-003</t>
-  </si>
-  <si>
     <t>TAS-012</t>
   </si>
   <si>
-    <t>TAS-002</t>
-  </si>
-  <si>
-    <t>TAS-008</t>
-  </si>
-  <si>
     <t>TAS-009</t>
   </si>
   <si>
-    <t>TAS-010</t>
-  </si>
-  <si>
-    <t>TAS-001</t>
+    <t>Lim Wei Jie</t>
+  </si>
+  <si>
+    <t>Tan Xiu Ying</t>
+  </si>
+  <si>
+    <t>Muhammad Hafiz</t>
   </si>
   <si>
     <t>Chloe Wong</t>
@@ -97,85 +106,112 @@
     <t>Hafiz Bin Aris</t>
   </si>
   <si>
+    <t>Aisha Binte Yusof</t>
+  </si>
+  <si>
+    <t>Darren Foo</t>
+  </si>
+  <si>
     <t>Raeanne Ong</t>
   </si>
   <si>
-    <t>Muhammad Hafiz</t>
-  </si>
-  <si>
     <t>Jordan Tan</t>
   </si>
   <si>
-    <t>Tan Xiu Ying</t>
-  </si>
-  <si>
-    <t>Aisha Binte Yusof</t>
-  </si>
-  <si>
-    <t>Darren Foo</t>
-  </si>
-  <si>
-    <t>Lim Wei Jie</t>
+    <t>2025-01-31</t>
   </si>
   <si>
     <t>2025-03-31</t>
   </si>
   <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
     <t>2025-04-30</t>
   </si>
   <si>
     <t>2025-06-30</t>
   </si>
   <si>
+    <t>2025-07-31</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
     <t>2025-09-30</t>
   </si>
   <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
     <t>2025-10-31</t>
   </si>
   <si>
     <t>2025-05-31</t>
   </si>
   <si>
-    <t>2025-07-31</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>2025-01-31</t>
+    <t>SGD 165.00</t>
+  </si>
+  <si>
+    <t>SGD 90.00</t>
+  </si>
+  <si>
+    <t>SGD 240.00</t>
+  </si>
+  <si>
+    <t>SGD 75.00</t>
+  </si>
+  <si>
+    <t>SGD 70.00</t>
+  </si>
+  <si>
+    <t>SGD 112.50</t>
+  </si>
+  <si>
+    <t>SGD 120.00</t>
+  </si>
+  <si>
+    <t>SGD 135.00</t>
+  </si>
+  <si>
+    <t>SGD 45.00</t>
+  </si>
+  <si>
+    <t>Paid</t>
   </si>
   <si>
     <t>Pending</t>
   </si>
   <si>
-    <t>Paid</t>
+    <t>PENDING</t>
+  </si>
+  <si>
+    <t>pend</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>2025-08-02</t>
+  </si>
+  <si>
+    <t>2025-09-01</t>
   </si>
   <si>
     <t>2025-10-04</t>
   </si>
   <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
     <t>2025-06-02</t>
   </si>
   <si>
-    <t>2025-08-02</t>
-  </si>
-  <si>
     <t>2025-04-01</t>
   </si>
   <si>
-    <t>2025-09-01</t>
-  </si>
-  <si>
     <t>2025-03-05</t>
   </si>
   <si>
-    <t>2025-02-05</t>
+    <t>Awaiting bank transfer</t>
   </si>
   <si>
     <t>No response from parent</t>
@@ -184,40 +220,34 @@
     <t>Note trailing space</t>
   </si>
   <si>
-    <t>Awaiting bank transfer</t>
-  </si>
-  <si>
-    <t>Invoice ID</t>
-  </si>
-  <si>
-    <t>Assignment ID</t>
-  </si>
-  <si>
-    <t>Student Name</t>
-  </si>
-  <si>
-    <t>Invoice Date</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>Payment Status</t>
-  </si>
-  <si>
-    <t>Payment Date</t>
-  </si>
-  <si>
-    <t>Notes</t>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,9 +306,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -576,43 +605,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="22.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
+    <col min="4" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
     <col min="8" max="8" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>64</v>
+      <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -628,14 +656,14 @@
       <c r="D2" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="1">
-        <v>75.0000</v>
+      <c r="E2" t="s">
+        <v>44</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="G2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -651,11 +679,14 @@
       <c r="D3" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="1">
-        <v>70.0000</v>
+      <c r="E3" t="s">
+        <v>45</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>54</v>
+      </c>
+      <c r="H3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -671,14 +702,14 @@
       <c r="D4" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="1">
-        <v>112.5000</v>
+      <c r="E4" t="s">
+        <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" t="s">
-        <v>55</v>
+        <v>53</v>
+      </c>
+      <c r="G4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -692,16 +723,16 @@
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="1">
-        <v>120.0000</v>
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" t="s">
-        <v>46</v>
+        <v>55</v>
+      </c>
+      <c r="H5" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -715,16 +746,13 @@
         <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="1">
-        <v>240.0000</v>
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>48</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -738,13 +766,16 @@
         <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="1">
-        <v>135.0000</v>
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>49</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>54</v>
+      </c>
+      <c r="H7" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -758,16 +789,16 @@
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="1">
-        <v>90.0000</v>
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" t="s">
-        <v>56</v>
+        <v>53</v>
+      </c>
+      <c r="G8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -775,137 +806,272 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="1">
-        <v>70.0000</v>
+      <c r="E9" t="s">
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G9" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="1">
-        <v>90.0000</v>
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>44</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
         <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="1">
-        <v>45.0000</v>
+        <v>41</v>
+      </c>
+      <c r="E11" t="s">
+        <v>50</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="1">
-        <v>165.0000</v>
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>46</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G12" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="1">
-        <v>165.0000</v>
+        <v>42</v>
+      </c>
+      <c r="E13" t="s">
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="1">
-        <v>165.0000</v>
-      </c>
-      <c r="F14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" t="s">
-        <v>53</v>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
